--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1662"/>
+  <dimension ref="A1:C1664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25356,6 +25356,28 @@
         <v>168</v>
       </c>
     </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr"/>
+      <c r="C1663" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr"/>
+      <c r="C1664" t="n">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1664"/>
+  <dimension ref="A1:C1666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25378,6 +25378,28 @@
         <v>169</v>
       </c>
     </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr"/>
+      <c r="C1665" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr"/>
+      <c r="C1666" t="n">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1664"/>
+  <dimension ref="A1:C1678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25378,6 +25378,215 @@
         <v>169</v>
       </c>
     </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr"/>
+      <c r="C1669" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr"/>
+      <c r="C1670" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr"/>
+      <c r="C1678" t="n">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1678"/>
+  <dimension ref="A1:C1680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25587,6 +25587,28 @@
         <v>170</v>
       </c>
     </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr"/>
+      <c r="C1679" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr"/>
+      <c r="C1680" t="n">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1680"/>
+  <dimension ref="A1:C1683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25609,6 +25609,39 @@
         <v>171</v>
       </c>
     </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr"/>
+      <c r="C1681" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr"/>
+      <c r="C1682" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr"/>
+      <c r="C1683" t="n">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1683"/>
+  <dimension ref="A1:C1707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25642,6 +25642,376 @@
         <v>172</v>
       </c>
     </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr"/>
+      <c r="C1699" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr"/>
+      <c r="C1700" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1683"/>
+  <dimension ref="A1:C1706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25642,6 +25642,350 @@
         <v>172</v>
       </c>
     </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr"/>
+      <c r="C1687" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr"/>
+      <c r="C1688" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr"/>
+      <c r="C1699" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr"/>
+      <c r="C1700" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>410</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1706"/>
+  <dimension ref="A1:C1708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25986,6 +25986,38 @@
         <v>410</v>
       </c>
     </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1708" t="n">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1708"/>
+  <dimension ref="A1:C1714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26018,6 +26018,99 @@
         <v>122</v>
       </c>
     </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1709" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1710" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1711" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1712" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1713" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1714" t="n">
+        <v>411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1714"/>
+  <dimension ref="A1:C1715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26111,6 +26111,22 @@
         <v>411</v>
       </c>
     </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="C1715" t="n">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1714"/>
+  <dimension ref="A1:C1695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24928,16 +24928,17 @@
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>referee</t>
         </is>
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t xml:space="preserve">lopez m 
+  esp </t>
         </is>
       </c>
       <c r="C1634" t="n">
-        <v>408</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1635">
@@ -24948,7 +24949,7 @@
       </c>
       <c r="B1635" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
@@ -24959,1156 +24960,957 @@
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B1636" t="inlineStr">
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio ramon sanchez pizjuan
   sevilla </t>
         </is>
       </c>
-      <c r="C1636" t="n">
+      <c r="C1664" t="n">
         <v>164</v>
       </c>
     </row>
-    <row r="1637">
-      <c r="A1637" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1637" t="inlineStr">
-        <is>
-          <t>AD5WKzF</t>
-        </is>
-      </c>
-      <c r="C1637" t="n">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="1638">
-      <c r="A1638" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1638" t="inlineStr">
-        <is>
-          <t>bs5KnIi</t>
-        </is>
-      </c>
-      <c r="C1638" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="1639">
-      <c r="A1639" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1639" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1639" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="1640">
-      <c r="A1640" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1640" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1640" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="1641">
-      <c r="A1641" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1641" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alvendiz l 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1641" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="1642">
-      <c r="A1642" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1642" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maeso f 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1642" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="1643">
-      <c r="A1643" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1643" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1643" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="1644">
-      <c r="A1644" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1644" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1644" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="1645">
-      <c r="A1645" t="inlineStr">
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B1645" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="C1645" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1646">
-      <c r="A1646" t="inlineStr">
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B1646" t="inlineStr">
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
         <is>
           <t xml:space="preserve">reale arena
   san sebastian </t>
         </is>
       </c>
-      <c r="C1646" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1647">
-      <c r="A1647" t="inlineStr">
+      <c r="C1679" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B1647" t="inlineStr">
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="C1681" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de mestalla
   valencia </t>
         </is>
       </c>
-      <c r="C1647" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1648">
-      <c r="A1648" t="inlineStr">
+      <c r="C1689" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B1648" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="C1648" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1649">
-      <c r="A1649" t="inlineStr">
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B1649" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
-        </is>
-      </c>
-      <c r="C1649" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1650">
-      <c r="A1650" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1650" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="C1650" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1651">
-      <c r="A1651" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1651" t="inlineStr">
+      <c r="B1691" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio benito villamarin
   sevilla </t>
         </is>
       </c>
-      <c r="C1651" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1652">
-      <c r="A1652" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1652" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="C1652" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="1653">
-      <c r="A1653" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1653" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1653" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="1654">
-      <c r="A1654" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1654" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vega a  c 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1654" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="1655">
-      <c r="A1655" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1655" t="inlineStr"/>
-      <c r="C1655" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="1656">
-      <c r="A1656" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1656" t="inlineStr"/>
-      <c r="C1656" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="1657">
-      <c r="A1657" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1657" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="C1657" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="1658">
-      <c r="A1658" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1658" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="C1658" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="1659">
-      <c r="A1659" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1659" t="inlineStr"/>
-      <c r="C1659" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="1660">
-      <c r="A1660" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1660" t="inlineStr"/>
-      <c r="C1660" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="1661">
-      <c r="A1661" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1661" t="inlineStr"/>
-      <c r="C1661" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="1662">
-      <c r="A1662" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1662" t="inlineStr"/>
-      <c r="C1662" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="1663">
-      <c r="A1663" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1663" t="inlineStr"/>
-      <c r="C1663" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="1664">
-      <c r="A1664" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1664" t="inlineStr"/>
-      <c r="C1664" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="1665">
-      <c r="A1665" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1665" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1665" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="1666">
-      <c r="A1666" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1666" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrera r 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1666" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="1667">
-      <c r="A1667" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1667" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1667" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="1668">
-      <c r="A1668" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1668" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1668" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="1669">
-      <c r="A1669" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1669" t="inlineStr"/>
-      <c r="C1669" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1670">
-      <c r="A1670" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1670" t="inlineStr"/>
-      <c r="C1670" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1671">
-      <c r="A1671" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1671" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="C1671" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1672">
-      <c r="A1672" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1672" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="C1672" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1673">
-      <c r="A1673" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1673" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="C1673" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1674">
-      <c r="A1674" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1674" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
-        </is>
-      </c>
-      <c r="C1674" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1675">
-      <c r="A1675" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1675" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="C1675" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1676">
-      <c r="A1676" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1676" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
-        </is>
-      </c>
-      <c r="C1676" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1677">
-      <c r="A1677" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1677" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="C1677" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1678">
-      <c r="A1678" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1678" t="inlineStr"/>
-      <c r="C1678" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="1679">
-      <c r="A1679" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1679" t="inlineStr"/>
-      <c r="C1679" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="1680">
-      <c r="A1680" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1680" t="inlineStr"/>
-      <c r="C1680" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="1681">
-      <c r="A1681" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1681" t="inlineStr"/>
-      <c r="C1681" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="1682">
-      <c r="A1682" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1682" t="inlineStr"/>
-      <c r="C1682" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="1683">
-      <c r="A1683" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1683" t="inlineStr"/>
-      <c r="C1683" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="1684">
-      <c r="A1684" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1684" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1684" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="1685">
-      <c r="A1685" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1685" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1685" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="1686">
-      <c r="A1686" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1686" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1686" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="1687">
-      <c r="A1687" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1687" t="inlineStr"/>
-      <c r="C1687" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="1688">
-      <c r="A1688" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1688" t="inlineStr"/>
-      <c r="C1688" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="1689">
-      <c r="A1689" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B1689" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="C1689" t="n">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="1690">
-      <c r="A1690" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1690" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1690" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="1691">
-      <c r="A1691" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1691" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
       <c r="C1691" t="n">
-        <v>121</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="B1692" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="C1692" t="n">
-        <v>121</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="B1693" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="C1693" t="n">
-        <v>121</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="C1694" t="n">
-        <v>121</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="C1695" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="1696">
-      <c r="A1696" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1696" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1696" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="1697">
-      <c r="A1697" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1697" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1697" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="1698">
-      <c r="A1698" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1698" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1698" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="1699">
-      <c r="A1699" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1699" t="inlineStr"/>
-      <c r="C1699" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="1700">
-      <c r="A1700" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1700" t="inlineStr"/>
-      <c r="C1700" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="1701">
-      <c r="A1701" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1701" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
-        </is>
-      </c>
-      <c r="C1701" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="1702">
-      <c r="A1702" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1702" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
-        </is>
-      </c>
-      <c r="C1702" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="1703">
-      <c r="A1703" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B1703" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
-        </is>
-      </c>
-      <c r="C1703" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="1704">
-      <c r="A1704" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1704" t="inlineStr">
-        <is>
-          <t>Ii1Om118</t>
-        </is>
-      </c>
-      <c r="C1704" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="1705">
-      <c r="A1705" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1705" t="inlineStr">
-        <is>
-          <t>Ii1Om118</t>
-        </is>
-      </c>
-      <c r="C1705" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="1706">
-      <c r="A1706" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1706" t="inlineStr">
-        <is>
-          <t>Ii1Om118</t>
-        </is>
-      </c>
-      <c r="C1706" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="1707">
-      <c r="A1707" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1707" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1707" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="1708">
-      <c r="A1708" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1708" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1708" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="1709">
-      <c r="A1709" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1709" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1709" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="1710">
-      <c r="A1710" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1710" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1710" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="1711">
-      <c r="A1711" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B1711" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="C1711" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="1712">
-      <c r="A1712" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1712" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="C1712" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="1713">
-      <c r="A1713" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1713" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="C1713" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="1714">
-      <c r="A1714" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B1714" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="C1714" t="n">
-        <v>411</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1695"/>
+  <dimension ref="A1:C1700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25913,6 +25913,86 @@
         <v>315</v>
       </c>
     </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1695"/>
+  <dimension ref="A1:C1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25913,6 +25913,99 @@
         <v>315</v>
       </c>
     </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1701"/>
+  <dimension ref="A1:C1706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26006,6 +26006,86 @@
         <v>408</v>
       </c>
     </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1706"/>
+  <dimension ref="A1:C1707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26086,6 +26086,22 @@
         <v>118</v>
       </c>
     </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1707"/>
+  <dimension ref="A1:C1708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26102,6 +26102,22 @@
         <v>165</v>
       </c>
     </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1708" t="n">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1708"/>
+  <dimension ref="A1:C1711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26118,6 +26118,51 @@
         <v>119</v>
       </c>
     </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="C1709" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="C1710" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="C1711" t="n">
+        <v>409</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1711"/>
+  <dimension ref="A1:C1712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26163,6 +26163,21 @@
         <v>409</v>
       </c>
     </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>YaDNxIRF</t>
+        </is>
+      </c>
+      <c r="C1712" t="n">
+        <v>410</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
